--- a/data/students.xlsx
+++ b/data/students.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,1713 +468,1748 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>stu002</t>
+          <t>stu001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1ED23IS002</t>
+          <t>1ED22CS001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vivaan</t>
+          <t>Aarav</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>vivaan@edumitra.com</t>
+          <t>aarav@edumitra.com</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$nVNqzfnfO2fM2TsHwLh3Tg$2r61/aev1YHItaF41j/hkQgOFejsYiYWwhamN0vNzEk</t>
+          <t>$pbkdf2-sha256$29000$AmBMac15LwWAEOL8//.fMw$Tw3cboQLlMiSKDIg3TG7PzH0jLMkYdv/Gz/KmUk3cmk</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>ISE</t>
+          <t>CSE</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>stu003</t>
+          <t>stu002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>1ED24EC003</t>
+          <t>1ED23IS002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Aditya</t>
+          <t>Vivaan</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>aditya@edumitra.com</t>
+          <t>vivaan@edumitra.com</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$t7YWYsz5HwOgdI6x9l4L4Q$tekcGAGqzxXllRKX9AcvHc6J3bpVNo.z0EA4lvo6ZzQ</t>
+          <t>$pbkdf2-sha256$29000$OSfEGANgzLlXyrm3lvJ.rw$CsDm0iT3fvu8mOruP4/fpSLE05OjfEbOZqVbnFIakpo</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>ISE</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>stu004</t>
+          <t>stu003</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1ED22ME004</t>
+          <t>1ED24EC003</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Vihaan</t>
+          <t>Aditya</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>vihaan@edumitra.com</t>
+          <t>aditya@edumitra.com</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$AABg7F0rpRRiLIXwPsd4Lw$AbSAKltHVU0AeP3Vnn60Y5ISMC4sJviwpE8wf9CkETs</t>
+          <t>$pbkdf2-sha256$29000$8J6zVuodA.AcAyBkDCGklA$2J3Ojl64ancwrVxtfMYabVqVAG2ulcvX/kZ5vZt1QC4</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>ECE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>stu005</t>
+          <t>stu004</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1ED23EE005</t>
+          <t>1ED22ME004</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Arjun</t>
+          <t>Vihaan</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>arjun@edumitra.com</t>
+          <t>vihaan@edumitra.com</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$RSjl/J8TorS29n6P0fq/Nw$Ocag6Iz9Yo7b5jwDrbFLqZV6vblXCe87tq/rNOvzmSc</t>
+          <t>$pbkdf2-sha256$29000$0Xqv1fq/N0ao1ToHQMgZAw$hkD9CY0k207kp3YLvUMirqFzUtRjpRWBfSgT8DRzlmA</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EEE</t>
+          <t>ME</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>stu006</t>
+          <t>stu005</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1ED24CE006</t>
+          <t>1ED23EE005</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sai</t>
+          <t>Arjun</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>sai@edumitra.com</t>
+          <t>arjun@edumitra.com</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$y3lPSSnlvHfuvVdKCQFAKA$mLWtqp6yNfmlLlHZqxINrFG7C8qb.Fxl31GIvlBiVvA</t>
+          <t>$pbkdf2-sha256$29000$55yzds75f2.t1ToHgPA.xw$ExLSSW9RLZVbYUDnM28dj9hTFB58.1E652GQ/D9xCe0</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>EEE</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>stu007</t>
+          <t>stu006</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>1ED22CS007</t>
+          <t>1ED24CE006</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Reyansh</t>
+          <t>Sai</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>reyansh@edumitra.com</t>
+          <t>sai@edumitra.com</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$a62VUiplrLV2DkFojTGG8A$g.eXjhGUQEBqv3CMch.Ls4G5Pfmsm03YkcK4xcAuaYk</t>
+          <t>$pbkdf2-sha256$29000$PAdgbG2tlfJ.r3VOifFeKw$ibPir0sVPdJ39dkIEDmZXzyrGEkKLCxwUc9UQoayU94</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>CE</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>stu008</t>
+          <t>stu007</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1ED23IS008</t>
+          <t>1ED22CS007</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Krishna</t>
+          <t>Reyansh</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>krishna@edumitra.com</t>
+          <t>reyansh@edumitra.com</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$KQXA2JuTkrKWcm7N.R.jVA$V78RZGbqKy/Axs6mRrNYsS3ji/trgiESSWUeZvyRZwY</t>
+          <t>$pbkdf2-sha256$29000$LIVQau2dkxJC6H1PaS1FiA$Ct1vWJLk.SPjoSi36U9rvJkpnEY0Gs.mfOGDpdvgmew</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>ISE</t>
+          <t>CSE</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>stu009</t>
+          <t>stu008</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1ED24EC009</t>
+          <t>1ED23IS008</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ishaan</t>
+          <t>Krishna</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>ishaan@edumitra.com</t>
+          <t>krishna@edumitra.com</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$PsfYO.d8D2FMqfXeW4vxfg$YCHdnjrYGzpD38/GgnsCdVdsaYT7fmHWziZ.MFBxQIo</t>
+          <t>$pbkdf2-sha256$29000$xjgHAAAA4Px/by1FCMEYww$KJ7lzdZ6TQXje9WFSe.4yjdwg21Fn90yNKx24FY2uL0</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>ISE</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>stu010</t>
+          <t>stu009</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>1ED22ME010</t>
+          <t>1ED24EC009</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Shaurya</t>
+          <t>Ishaan</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>shaurya@edumitra.com</t>
+          <t>ishaan@edumitra.com</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$S.mds3bOOWcM4ZwT4vxfiw$F70aCyADwC6mKebjzDnxRoHFZb3nYSN3/ZxVkEgKLMc</t>
+          <t>$pbkdf2-sha256$29000$o3SOUco5J.RcK0XoPWcM4Q$uUiTFl0/Pc4l3Wqcup/kCFg.ri3wA9VuwrXOHXtFRYk</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>ECE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>stu011</t>
+          <t>stu010</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>1ED23EE011</t>
+          <t>1ED22ME010</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Ananya</t>
+          <t>Shaurya</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ananya@edumitra.com</t>
+          <t>shaurya@edumitra.com</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$J0QIAcBYC8GY855T6t3bew$T8QmJDacsO6AUJYNGxDsSE9v57sIV/fPZnfdOG3zaR0</t>
+          <t>$pbkdf2-sha256$29000$RGjt3buX0vqfUwrh3LuXcg$uXniYPGNjGTZlgb1xcR7CuqXpmvpYdTQsHp7TPdJfjQ</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>EEE</t>
+          <t>ME</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>stu012</t>
+          <t>stu011</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1ED24CE012</t>
+          <t>1ED23EE011</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Diya</t>
+          <t>Ananya</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>diya@edumitra.com</t>
+          <t>ananya@edumitra.com</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$vtda6917D4EQohQi5HwvxQ$DST7fnnGrcAOcs5p4LEAIaPHT3mtHhADhk7DiUyIqPk</t>
+          <t>$pbkdf2-sha256$29000$UUqpdY4x5pxTqpVyTklJ6Q$6.MDRPJA3vvV/qsh/RAeLOSrAw9J5NaSSN3bPFtQTro</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>EEE</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>stu013</t>
+          <t>stu012</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>1ED22CS013</t>
+          <t>1ED24CE012</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Myra</t>
+          <t>Diya</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>myra@edumitra.com</t>
+          <t>diya@edumitra.com</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$TMl5by2ldO4951zL.X8vhQ$gnY198x1Dec.ciUSPyZXBdjsfMum6rAfdrKocT9rTdE</t>
+          <t>$pbkdf2-sha256$29000$mtP637t3bq31XkvJuXdO6Q$7DkKGmciLPqNs1IT1W8RfPQ/KQ32mcUconH5HJ.4Aac</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>CE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>stu014</t>
+          <t>stu013</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1ED23IS014</t>
+          <t>1ED22CS013</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Sara</t>
+          <t>Myra</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>sara@edumitra.com</t>
+          <t>myra@edumitra.com</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$Z.y9l5LyXqv1XgthTMlZSw$eoPkZIc/1jMfmEJYuRQibnZyPHTwcUCgQiB6ZGAfWO8</t>
+          <t>$pbkdf2-sha256$29000$Qeg95/z/fy.llNLaO4fQGg$Ke9qiERkoQozgC0Raib7cMvwZab88tJsamk3crkm9Co</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>ISE</t>
+          <t>CSE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>stu015</t>
+          <t>stu014</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1ED24EC015</t>
+          <t>1ED23IS014</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Aadhya</t>
+          <t>Sara</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>aadhya@edumitra.com</t>
+          <t>sara@edumitra.com</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$ybn3fq.11hqDkFJq7b13jg$c97gBysDFk6rvmzOrCvymnGQpGnkUx7vuT3YwujOjvc</t>
+          <t>$pbkdf2-sha256$29000$z/mf01prjbHWWus9B2AMQQ$Rotns9pHcC9wRTRT8zclSxq13BRhAVoFUeQx2.n9V1g</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>ISE</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>stu016</t>
+          <t>stu015</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>1ED22ME016</t>
+          <t>1ED24EC015</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Ira</t>
+          <t>Aadhya</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>ira@edumitra.com</t>
+          <t>aadhya@edumitra.com</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$kfI.h7DW.p9zbi3lvJeSUg$CXZ8.OEo/HDrL5Q71MyhdsAw1DHnznp2/rPD85wGIdc</t>
+          <t>$pbkdf2-sha256$29000$ZQyhVCrlnHOulZIS4txbSw$96Zoni6K8Fe4sVVnSrUgpV.Kt9ol3fv9LbDQjVZ9M8o</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>ECE</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>stu017</t>
+          <t>stu016</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1ED23EE017</t>
+          <t>1ED22ME016</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Anika</t>
+          <t>Ira</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>anika@edumitra.com</t>
+          <t>ira@edumitra.com</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$0brXmrN2jhHi3HvPubcWYg$R5ReeUtpEUq60hli9cvSnahNRnaavANCoyXDwJ7zBkc</t>
+          <t>$pbkdf2-sha256$29000$ac15b.19D2FMCeEcw1jrvQ$yL.hsyUXUkDSICv3.LLFbcY/1vHCqsV.ioQsQZFPMnc</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>EEE</t>
+          <t>ME</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>stu018</t>
+          <t>stu017</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1ED24CE018</t>
+          <t>1ED23EE017</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Priya</t>
+          <t>Anika</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>priya@edumitra.com</t>
+          <t>anika@edumitra.com</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$3Fvr3bt3DmFsDaG0NmYMgQ$OtZvwVHHnWj.pzIel2AuL7IYfDcPX0cdSw6CWZzB4.Q</t>
+          <t>$pbkdf2-sha256$29000$7b1XyjlnzHlvjbE2BgAAoA$6lfwKomsJq1Tl4idntYPo8ViYIt1IXFez6pxJ3qaa9A</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>EEE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>stu019</t>
+          <t>stu018</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>1ED22CS019</t>
+          <t>1ED24CE018</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Kavya</t>
+          <t>Priya</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>kavya@edumitra.com</t>
+          <t>priya@edumitra.com</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$BsCY03pvbQ2htDamtFYqZQ$S1DZ8xo79PUnmrep6lQIp2TfXFIJ2GHl5fReiZE4qyE</t>
+          <t>$pbkdf2-sha256$29000$JuRci5FyTilFaI3xPscYow$QjAZT7M8alolZ5I2WRx5UhltTysPGZx9mzd52z/kSww</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>CE</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>stu020</t>
+          <t>stu019</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>1ED23IS020</t>
+          <t>1ED22CS019</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Riya</t>
+          <t>Kavya</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>riya@edumitra.com</t>
+          <t>kavya@edumitra.com</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$Y0wpJYTw3tv7/x8DQKg15g$J3v0JCpVKYzclZgzJMsqbqCWSBygXAbJdP4YBbR4voc</t>
+          <t>$pbkdf2-sha256$29000$53yvtTZmDCGk9H4PobR2jg$jslVBCTr2emTxwUmqS9OPntuFT1CkezzkJ5gQSPCBD8</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>ISE</t>
+          <t>CSE</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>stu021</t>
+          <t>stu020</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>1ED24EC021</t>
+          <t>1ED23IS020</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Rohan</t>
+          <t>Riya</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>rohan@edumitra.com</t>
+          <t>riya@edumitra.com</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$fm/NmRNCiLH2HuN8r1WqFQ$mSK08PxXvla3XSNI9WjWkCnvm6vNOwLKkMNg9WrAktY</t>
+          <t>$pbkdf2-sha256$29000$i5HyPuccQwhhzHnv/X/vXQ$addvxU8sOHE.13oUeu9NARiKbD3XiXAbubZiqBZpuC0</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>ISE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>stu022</t>
+          <t>stu021</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1ED22ME022</t>
+          <t>1ED24EC021</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Karthik</t>
+          <t>Rohan</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>karthik@edumitra.com</t>
+          <t>rohan@edumitra.com</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$hXCOMQbAWKsVovQ.x/hfyw$MRAlV8C4vmBXtnM4coIdG2Iss4JO5iRcZdcABKoDQQg</t>
+          <t>$pbkdf2-sha256$29000$Uar1/l.rVYqx1vrfW8v5Hw$ZoWiYfFt.6R.UfA3VXVphp1tJZLnK5gPRR6NE61stRg</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>ECE</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>stu023</t>
+          <t>stu022</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>1ED23EE023</t>
+          <t>1ED22ME022</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Deepak</t>
+          <t>Karthik</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>deepak@edumitra.com</t>
+          <t>karthik@edumitra.com</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$U4pxrtXaew9BKKUUAkBIKQ$C28BBD8CO5fgAIRFE71DQtRVIphd0BWJvNV5VclSxnc</t>
+          <t>$pbkdf2-sha256$29000$KeVcK8W4997bWwtBiHHuHQ$nVhA.j6PjWCFSQjG9dJ0b4BAuhHPrJWQ.uzAgRmczgU</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>EEE</t>
+          <t>ME</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>stu024</t>
+          <t>stu023</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1ED24CE024</t>
+          <t>1ED23EE023</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Nikhil</t>
+          <t>Deepak</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>nikhil@edumitra.com</t>
+          <t>deepak@edumitra.com</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$ixHC.P8f4zxHaG1NybkXgg$myiziPrtz.RixBjwGTJMyNiXCIshr0RBxQdf6VhSiKY</t>
+          <t>$pbkdf2-sha256$29000$kXLuPSeEMMbY.3/vXYvROg$OhRnisqHBpG75UZI1Hloe6T22vbT3TYyck2mflRBe2g</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>EEE</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>stu025</t>
+          <t>stu024</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>1ED22CS025</t>
+          <t>1ED24CE024</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Rahul</t>
+          <t>Nikhil</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>rahul@edumitra.com</t>
+          <t>nikhil@edumitra.com</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$OCcEAOBcay3lPEdorXUOgQ$uTTCNZXQR8gPrSGmC4jPV08v.cR6raeigc7f2Zv4KXw</t>
+          <t>$pbkdf2-sha256$29000$3PufEyIE4LwXghAi5FwrRQ$v2thb/sH0.8raw3UvR/GWqs/FHsD8zKOPDE.gj9tIl4</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>CE</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>stu026</t>
+          <t>stu025</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1ED23IS026</t>
+          <t>1ED22CS025</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sneha</t>
+          <t>Rahul</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>sneha@edumitra.com</t>
+          <t>rahul@edumitra.com</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$j/F.712Lce49p9Q6R4jxvg$2Z1v3fIdVmvu/k80HEzva9dWtQbhGNTj/9XYu9zUIGw</t>
+          <t>$pbkdf2-sha256$29000$/79XijGmtJZyLmUMAQCAkA$u6b8MQ/WBAK7s18t8cQeaSoW0IPRuIySAi.4huJG1zA</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>ISE</t>
+          <t>CSE</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>stu027</t>
+          <t>stu026</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1ED24EC027</t>
+          <t>1ED23IS026</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pooja</t>
+          <t>Sneha</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>pooja@edumitra.com</t>
+          <t>sneha@edumitra.com</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$CQFgLEUoBeB8TwkhxNj7nw$h.RpQfJf1BgLpFSIROgpN/cApP5rjuumiUQuD.Gl9y4</t>
+          <t>$pbkdf2-sha256$29000$V.p9bw3h/H.v1fo/51xrzQ$W5VkgT.M.TWx2o0HLE2LE0/nYTf.G8C6.84zd6U7/.c</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>ISE</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>stu028</t>
+          <t>stu027</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1ED22ME028</t>
+          <t>1ED24EC027</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Meera</t>
+          <t>Pooja</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>meera@edumitra.com</t>
+          <t>pooja@edumitra.com</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$B2BszXmv1RpjLGXsfS9FCA$aSibrporpxlSSgPh8j0SxWjXXzsuqKiAvf9Yt0sMuSE</t>
+          <t>$pbkdf2-sha256$29000$8l5LScn5v5cSwhjj/D.nVA$fjeXjXxp0m9RT2sGwAur0OaMxoXO/7PEg3VaoJvyLUI</t>
         </is>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>ECE</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>stu029</t>
+          <t>stu028</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>1ED23EE029</t>
+          <t>1ED22ME028</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Lakshmi</t>
+          <t>Meera</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>lakshmi@edumitra.com</t>
+          <t>meera@edumitra.com</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$/38PwXhPaY0RohSCMOacEw$tQZaNb/kgBeSXNydJw/RGvDMcxRVh4nlYsbZTxarbdc</t>
+          <t>$pbkdf2-sha256$29000$OMeYcy5FCEGI0ToHAMCYcw$GNxEpYxA40Y2xBiG9SNT8OzTuCijyf4RJuI.i4n0foI</t>
         </is>
       </c>
       <c r="F29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>EEE</t>
+          <t>ME</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>stu030</t>
+          <t>stu029</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>1ED24CE030</t>
+          <t>1ED23EE029</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Nandini</t>
+          <t>Lakshmi</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>nandini@edumitra.com</t>
+          <t>lakshmi@edumitra.com</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$by0FoJRyLoUwZkxpbQ2htA$DyYZvOQUh3KGDcRg05vVrqHuwYjDlxdWzir0jvPZyJY</t>
+          <t>$pbkdf2-sha256$29000$AWAMAcDYGwNgrFVKSSkFYA$yM0SFBw/tlPqcxVblb6QACcmD/ddiCzygAOryKGwj5g</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>EEE</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>stu031</t>
+          <t>stu030</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1ED22CS031</t>
+          <t>1ED24CE030</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Amit</t>
+          <t>Nandini</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>amit@edumitra.com</t>
+          <t>nandini@edumitra.com</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$7J3znlPqPQdAiDHmPCfknA$GvwzdaS7Mo0me87rtrflQomi75lUk7jvYa0JfmnIHVg</t>
+          <t>$pbkdf2-sha256$29000$cQ6h1Fqr1XrP.b.XEoLwPg$gpJuuHzPFckVJzyUX1TZvpVpEsKcL8nemsyt3gXO37A</t>
         </is>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>CE</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>stu032</t>
+          <t>stu031</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>1ED23IS032</t>
+          <t>1ED22CS031</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Suresh</t>
+          <t>Amit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>suresh@edumitra.com</t>
+          <t>amit@edumitra.com</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$M6a0lhICYCzFOMcY45yTcg$66ggHRNai0..rCdoy5XC4zqHW5yrMq7PQLlyeeB9XOM</t>
+          <t>$pbkdf2-sha256$29000$iRGCkHKuFULI2ZuTMqbUug$/3ZSwUWOi.zdrQw5wbvO/bZg6dpJBbii8J9fMW1la2Q</t>
         </is>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>ISE</t>
+          <t>CSE</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>stu033</t>
+          <t>stu032</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1ED24EC033</t>
+          <t>1ED23IS032</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Vijay</t>
+          <t>Suresh</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>vijay@edumitra.com</t>
+          <t>suresh@edumitra.com</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$3pvTeq/VGmOM8Z6zFmLMmQ$d6hgQx1D20mwS3TvI6Wg4eyNfsEjBXBzXAUHBfumiw8</t>
+          <t>$pbkdf2-sha256$29000$qXXu/V8rhTAmpNTa23uP8Q$8J4PNiMbb..LU.DEM/nLjKhnFzclTUOdbApfunj3tR4</t>
         </is>
       </c>
       <c r="F33" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>ISE</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>stu034</t>
+          <t>stu033</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1ED22ME034</t>
+          <t>1ED24EC033</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Ganesh</t>
+          <t>Vijay</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>ganesh@edumitra.com</t>
+          <t>vijay@edumitra.com</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$dg7BmLPWOsf4H2OM0boXQg$oyuF0M9h9web0F6KP7QZBjOvTjg8sO3b/rPSWA5KgcU</t>
+          <t>$pbkdf2-sha256$29000$YIwRAmDsXcu51xqj9L6X0g$ve13VDH.znPYC0o2.W/lrp/YRck9a5/kINzOlbZls8k</t>
         </is>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>ECE</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>stu035</t>
+          <t>stu034</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>1ED23EE035</t>
+          <t>1ED22ME034</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Harsha</t>
+          <t>Ganesh</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>harsha@edumitra.com</t>
+          <t>ganesh@edumitra.com</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$3XvPudcao3RuDSEEYOxd6w$HrYOMh2em/6GnJdBoKlPxMRPv.pEUKegIq9OHzGVZ2U</t>
+          <t>$pbkdf2-sha256$29000$yLm39l5rjdHam1MKgbD2Xg$vcfIutQz8BvX3vyf7ixJIGcp2dCt28yYNa0Whr6NNDE</t>
         </is>
       </c>
       <c r="F35" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>EEE</t>
+          <t>ME</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>stu036</t>
+          <t>stu035</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1ED24CE036</t>
+          <t>1ED23EE035</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Divya</t>
+          <t>Harsha</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>divya@edumitra.com</t>
+          <t>harsha@edumitra.com</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$AaCUcg7h3PufU0rpfQ/B2A$U2DoQ9oEAgJM79UfegvLKJqD8efIo0/Ped7hVAjT01g</t>
+          <t>$pbkdf2-sha256$29000$ImTMmdMag9C6lzLm3Nu71w$LGxi1PuJlWeXT9cJZbSN9/pwLSeKAHUaO9Lh2GbvzI4</t>
         </is>
       </c>
       <c r="F36" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>EEE</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>stu037</t>
+          <t>stu036</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1ED22CS037</t>
+          <t>1ED24CE036</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Rashmi</t>
+          <t>Divya</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>rashmi@edumitra.com</t>
+          <t>divya@edumitra.com</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$dE7JeY8xxvi/l7IWopQSog$cSccshc8Sho0nWQq31OG3YFSTj6du8eRY4fiasEXu88</t>
+          <t>$pbkdf2-sha256$29000$qzUmZMy5N6b0XqvVuheiVA$/5TneJGL.dot.JRHVswMkjUV8q1LaihAYTM9oisXIIQ</t>
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>CE</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>stu038</t>
+          <t>stu037</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>1ED23IS038</t>
+          <t>1ED22CS037</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Swati</t>
+          <t>Rashmi</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>swati@edumitra.com</t>
+          <t>rashmi@edumitra.com</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$bi1FqPV.T6k1hvAeQ2jtvQ$e29wU5daDZ17BQU87.t48KkVxHF0ljyiJihsMkOobK8</t>
+          <t>$pbkdf2-sha256$29000$6X3vPSekdG5NyZmzlpKS0g$dTYUXbQxXAgkrFmJx3vkail9H1PAZME9vmI5y/dzmVc</t>
         </is>
       </c>
       <c r="F38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>ISE</t>
+          <t>CSE</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>stu039</t>
+          <t>stu038</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1ED24EC039</t>
+          <t>1ED23IS038</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Pallavi</t>
+          <t>Swati</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>pallavi@edumitra.com</t>
+          <t>swati@edumitra.com</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$h3CuVUpJCYFQ6r13zrkXQg$u253coMAZ6dHfyORLfs7uj6q.q.1gwhgCLacQyiDM.Q</t>
+          <t>$pbkdf2-sha256$29000$IUTIOcdYS6mV8r7X2tvbOw$o5qCU3P6gDfnA6sCkJEJnIDi47YdJ2oLHRBDL1.myfQ</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>ISE</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>stu040</t>
+          <t>stu039</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1ED22ME040</t>
+          <t>1ED24EC039</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tanvi</t>
+          <t>Pallavi</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>tanvi@edumitra.com</t>
+          <t>pallavi@edumitra.com</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$RmiNUYrRWuvd27sXYkzpPQ$uc7wTxJeog6mGMnh6Iv2MT.6MYGhj8ATTYCygOft.4I</t>
+          <t>$pbkdf2-sha256$29000$HwPgfA9B6P1/z9kbYyyFsA$9rDBHb.KlNQEefeIeMfx78A2yDhUMuzHkpTgvx8li0k</t>
         </is>
       </c>
       <c r="F40" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>ECE</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>stu041</t>
+          <t>stu040</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1ED23EE041</t>
+          <t>1ED22ME040</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Akash</t>
+          <t>Tanvi</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>akash@edumitra.com</t>
+          <t>tanvi@edumitra.com</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$plSKUcqZ01oL4XwP4bwX4g$9PcOsmtA8E1SkT8.cXafiCmLDcK6FCfLZg0MmDngMe8</t>
+          <t>$pbkdf2-sha256$29000$pjSmlHKOkXLOeQ9BaG0tpQ$.js3/1GshvDRac4vBBFyTIuXsyFoHt0RNkwdBLAB2DU</t>
         </is>
       </c>
       <c r="F41" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>EEE</t>
+          <t>ME</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>stu042</t>
+          <t>stu041</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1ED24CE042</t>
+          <t>1ED23EE041</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Pranav</t>
+          <t>Akash</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>pranav@edumitra.com</t>
+          <t>akash@edumitra.com</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$ixFCSAkhJESIMab0fi.FUA$Bx9ym29k2.kfZhDDjHNVjr3YCMyMe5d9w8gpQMOozXQ</t>
+          <t>$pbkdf2-sha256$29000$XMtZq7WW8j6HcI5RKgXgfA$uyCbiANjNm.K42X01V3hzR.MaZ6.HmVg.7m/uByx45c</t>
         </is>
       </c>
       <c r="F42" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>EEE</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>stu043</t>
+          <t>stu042</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1ED22CS043</t>
+          <t>1ED24CE042</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Siddharth</t>
+          <t>Pranav</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>siddharth@edumitra.com</t>
+          <t>pranav@edumitra.com</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$0rqXstbam5MSYizl/D9n7A$fCKr1mUJI./7/8SWPDg0s4.ESvgep3mSj0dilw/Y0EM</t>
+          <t>$pbkdf2-sha256$29000$ei/lPCfkfC.FMIYw5hxjLA$7if/M38ugx4NUXt4S1nLEF.FiavxSJMcRGepXNPUBDU</t>
         </is>
       </c>
       <c r="F43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>CE</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>stu044</t>
+          <t>stu043</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1ED23IS044</t>
+          <t>1ED22CS043</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Varun</t>
+          <t>Siddharth</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>varun@edumitra.com</t>
+          <t>siddharth@edumitra.com</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$yrm3tpZyjlEqJWSsNQaAMA$9E5RKah9DKxK.7sCL7Iv/4HABqI.Wz58MGyPh/Pucfc</t>
+          <t>$pbkdf2-sha256$29000$snYu5TxHiPF.b6219h4DQA$NxGPFlQJBlhdnEdsCy6vuYr/Cb.IPGJaDttG1zohov8</t>
         </is>
       </c>
       <c r="F44" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>ISE</t>
+          <t>CSE</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>stu045</t>
+          <t>stu044</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1ED24EC045</t>
+          <t>1ED23IS044</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Tarun</t>
+          <t>Varun</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>tarun@edumitra.com</t>
+          <t>varun@edumitra.com</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$vff.39t7Twnh/N8bI0SIcQ$3NDg9Ryl5TMImADoBlNrbGQeJSOa4ud9c3VUMSD/hYI</t>
+          <t>$pbkdf2-sha256$29000$hBCilPJey9n7P0dIae29Nw$OrZalsOVal31uyda754/jO5Bz..xfpf//bhzuc.UgLk</t>
         </is>
       </c>
       <c r="F45" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>ECE</t>
+          <t>ISE</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>stu046</t>
+          <t>stu045</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>1ED22ME046</t>
+          <t>1ED24EC045</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Neha</t>
+          <t>Tarun</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>neha@edumitra.com</t>
+          <t>tarun@edumitra.com</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$lxJibG3NOae0tnYOwbj3/g$a4I5JMQOgm0likJm/Ubiejw9JyIzK8wQWcG7Ji6ObQs</t>
+          <t>$pbkdf2-sha256$29000$ZCyFcK51jhHCmHMOgTAmZA$.HGK2xFRn0Oz7dpv71CdhMpluavDWLoJ6Cuupe2jf1c</t>
         </is>
       </c>
       <c r="F46" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>ME</t>
+          <t>ECE</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>stu047</t>
+          <t>stu046</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>1ED23EE047</t>
+          <t>1ED22ME046</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Shruti</t>
+          <t>Neha</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>shruti@edumitra.com</t>
+          <t>neha@edumitra.com</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$15oT4hxDiFHqXav1HiPE.A$Mg6fj8lxe9Cdo02JIv6oy8iwgEmzMbmRpLvpPZmNH3k</t>
+          <t>$pbkdf2-sha256$29000$kfJ.r7X2XkvpnTMGwHgP4Q$Yl2JaFlplwQSBa2pbcqjVmrgd1sVGTdbE4AeD2ktFyw</t>
         </is>
       </c>
       <c r="F47" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>EEE</t>
+          <t>ME</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>stu048</t>
+          <t>stu047</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1ED24CE048</t>
+          <t>1ED23EE047</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bhavana</t>
+          <t>Shruti</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>bhavana@edumitra.com</t>
+          <t>shruti@edumitra.com</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$.b835jwHAECotdb6f8.51w$Lf7iDDokCy0aS5LHV7IUt54snvOAdoUnDmTmggrf.J4</t>
+          <t>$pbkdf2-sha256$29000$pNQag9Aa4zxnTKk1hhDC2A$PusuQz4sQrPVX.MbaMFLQkF07966UL3VA2IKsCyT2UM</t>
         </is>
       </c>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>CE</t>
+          <t>EEE</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>stu049</t>
+          <t>stu048</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1ED22CS049</t>
+          <t>1ED24CE048</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Chaitra</t>
+          <t>Bhavana</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>chaitra@edumitra.com</t>
+          <t>bhavana@edumitra.com</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>$pbkdf2-sha256$29000$894bY.yds/YeQ4hxzhnDuA$UP1DcOH/kEb/v/rH8XmymJHMgYo5T5LfJn8hi4WhVGM</t>
+          <t>$pbkdf2-sha256$29000$wLhX6h1jTAkhpJSS8r6Xsg$3pddBoW.9KDry.jKrIENBfgUZMSzhvdix79aJwVip5Q</t>
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>CSE</t>
+          <t>CE</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
+          <t>stu049</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>1ED22CS049</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Chaitra</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>chaitra@edumitra.com</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>$pbkdf2-sha256$29000$UArhHIMQ4nxPCQFACEFoLQ$Nlnd7hY2S4Pi7BclAR6z/geKs.wbIm6J8MCa6eyHW04</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>3</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>CSE</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
           <t>stu050</t>
         </is>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B51" t="inlineStr">
         <is>
           <t>1ED23IS050</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>Keerthi</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>keerthi@edumitra.com</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>$pbkdf2-sha256$29000$z1mLEeL8HyMEQAhB6L03pg$kg.he4fgkuzK7w322UZHDrh3IcEddrHfV4rio8di5aY</t>
-        </is>
-      </c>
-      <c r="F50" t="n">
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>$pbkdf2-sha256$29000$FaKUktJ6T4nx/j/n/H9PqQ$QnsX.kkawBWFzYF4b1saZjOJTHOkipPriQ4H34eezBg</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
         <v>4</v>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>ISE</t>
         </is>
